--- a/data/trans_orig/IP05A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88828</t>
+          <t>88934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100333</t>
+          <t>100733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64746</t>
+          <t>64587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78582</t>
+          <t>78991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68643</t>
+          <t>68590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>82989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137307</t>
+          <t>137223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157597</t>
+          <t>158608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19616</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>45392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66026</t>
+          <t>66381</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63631</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65436</t>
+          <t>66050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132797</t>
+          <t>131124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137317</t>
+          <t>137313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60699</t>
+          <t>60371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75166</t>
+          <t>74863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131144</t>
+          <t>129989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142604</t>
+          <t>142607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>33804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>48819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98592</t>
+          <t>98780</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109069</t>
+          <t>108693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111020</t>
+          <t>110670</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121655</t>
+          <t>121551</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116628</t>
+          <t>116744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>128068</t>
+          <t>128103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>231844</t>
+          <t>231763</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>247403</t>
+          <t>247448</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>99148</t>
+          <t>99066</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>117731</t>
+          <t>117490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>108482</t>
+          <t>108316</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>126483</t>
+          <t>126855</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>211935</t>
+          <t>212460</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>238294</t>
+          <t>238171</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>50064</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>32777</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>51469</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96563</t>
+          <t>96388</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,82 +4166,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>9662</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>16866</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>9049</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>10708</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>16993</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>537555</t>
+          <t>536907</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>569528</t>
+          <t>570037</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>576466</t>
+          <t>575875</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>609015</t>
+          <t>607924</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1122109</t>
+          <t>1121239</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1169005</t>
+          <t>1168600</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>96849</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>195093</t>
+          <t>193510</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>239113</t>
+          <t>238382</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>42188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>50917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>47187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>93384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105944</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78817</t>
+          <t>79214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>92183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78606</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93655</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163783</t>
+          <t>162974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182472</t>
+          <t>182265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29092</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44739</t>
+          <t>44756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62677</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68178</t>
+          <t>67551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>65649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>70588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131090</t>
+          <t>131215</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137454</t>
+          <t>138034</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>70199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76838</t>
+          <t>76459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130473</t>
+          <t>130098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144427</t>
+          <t>143908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54829</t>
+          <t>55114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69084</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54814</t>
+          <t>54784</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55692</t>
+          <t>55440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>59810</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>113869</t>
+          <t>113886</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>127500</t>
+          <t>126935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>135866</t>
+          <t>135753</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135428</t>
+          <t>134050</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142214</t>
+          <t>142124</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>265894</t>
+          <t>266042</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>276784</t>
+          <t>276680</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>134892</t>
+          <t>134655</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>149209</t>
+          <t>148690</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>138833</t>
+          <t>139282</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>154650</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>279644</t>
+          <t>278843</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>299987</t>
+          <t>299114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29285</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>54497</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>609691</t>
+          <t>606861</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>638790</t>
+          <t>636757</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>644218</t>
+          <t>643260</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>673669</t>
+          <t>674148</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1262228</t>
+          <t>1258883</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1303918</t>
+          <t>1300786</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>89376</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>93439</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>130620</t>
+          <t>133908</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>171065</t>
+          <t>172665</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>47924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84540</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99737</t>
+          <t>99986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>59927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75473</t>
+          <t>76970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87808</t>
+          <t>88096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136657</t>
+          <t>136784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158557</t>
+          <t>159461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44853</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38183</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58228</t>
+          <t>58013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>65291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>60139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67219</t>
+          <t>67260</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120465</t>
+          <t>120912</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131023</t>
+          <t>131627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69108</t>
+          <t>68890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73114</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124379</t>
+          <t>125850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139493</t>
+          <t>139807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33402</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41783</t>
+          <t>41798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69988</t>
+          <t>69415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80412</t>
+          <t>80255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49214</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>50534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>56965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102397</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109908</t>
+          <t>109973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106894</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121384</t>
+          <t>121694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103465</t>
+          <t>103041</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118836</t>
+          <t>119058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>216135</t>
+          <t>215619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>236954</t>
+          <t>236864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35910</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>142144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>154331</t>
+          <t>154295</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>148161</t>
+          <t>147867</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>160453</t>
+          <t>160045</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>294860</t>
+          <t>294427</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>311569</t>
+          <t>311610</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39834</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>577559</t>
+          <t>577506</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>608914</t>
+          <t>606699</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>605382</t>
+          <t>605307</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>636797</t>
+          <t>637545</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1191205</t>
+          <t>1192871</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1237713</t>
+          <t>1236750</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>81105</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>155021</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>194852</t>
+          <t>193166</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,47 +13337,47 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>41328</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>39247</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>63105</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>68901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148063</t>
+          <t>147503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45735</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114615</t>
+          <t>114242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104148</t>
+          <t>103098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117995</t>
+          <t>117989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130569</t>
+          <t>128494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227992</t>
+          <t>227183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79151</t>
+          <t>86380</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122358</t>
+          <t>124572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48911</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55428</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63338</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107463</t>
+          <t>107728</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>117554</t>
+          <t>117575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53123</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64460</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>67907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76484</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126624</t>
+          <t>125936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139479</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19163</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68455</t>
+          <t>68728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>74255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45163</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>48682</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>55289</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93069</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>99670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99496</t>
+          <t>99590</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112712</t>
+          <t>112905</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>122720</t>
+          <t>122413</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139146</t>
+          <t>138165</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>226585</t>
+          <t>226908</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>247664</t>
+          <t>247520</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>120882</t>
+          <t>121144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128788</t>
+          <t>128824</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>145118</t>
+          <t>143952</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>153985</t>
+          <t>153676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>269324</t>
+          <t>269399</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>281178</t>
+          <t>281192</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>509684</t>
+          <t>488058</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>612621</t>
+          <t>612787</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>687322</t>
+          <t>685248</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>713034</t>
+          <t>713032</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1181727</t>
+          <t>1194894</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1315168</t>
+          <t>1316579</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>141791</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
